--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitionerLocationOrganization.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitionerLocationOrganization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T06:41:33+00:00</t>
+    <t>2024-01-12T11:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayPractitionerLocationOrganization.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayPractitionerLocationOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T11:46:53+00:00</t>
+    <t>2024-01-12T11:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
